--- a/src/attributions/attributions_ig_traj_316.xlsx
+++ b/src/attributions/attributions_ig_traj_316.xlsx
@@ -2137,25 +2137,25 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03861353294707094</v>
+        <v>0.07878244022075791</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.005276532427423505</v>
+        <v>-0.01433291670181762</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.02539236421187406</v>
+        <v>-0.06050775472690802</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -2164,28 +2164,28 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01379460874812149</v>
+        <v>0.06887367126451684</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.005671419435010896</v>
+        <v>-0.01242083035628012</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.01989289377470765</v>
+        <v>-0.03865342499630639</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>-0</v>
@@ -2194,52 +2194,52 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.253929655144949e-05</v>
+        <v>0.005741758679384597</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002927022325143602</v>
+        <v>0.02468698060889571</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.004727342391754981</v>
+        <v>0.01311719015414855</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.007052126242695159</v>
+        <v>-0.04746979782117378</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.02310117333913242</v>
+        <v>-0.06042254266747742</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.0008527938949992792</v>
+        <v>-0.04141182190417277</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
         <v>-0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.006168509468720757</v>
+        <v>-0.003483922094736084</v>
       </c>
       <c r="AM4" t="n">
         <v>-0</v>
@@ -2257,13 +2257,13 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01142102683163243</v>
+        <v>-0.03617283961864123</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.01092719860538359</v>
+        <v>-0.03814812863823752</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2275,88 +2275,88 @@
         <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.05470647164513908</v>
+        <v>0.2781571733761675</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.001846825692363793</v>
+        <v>-0.0417096515441903</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.03964168295701465</v>
+        <v>-0.06991232443288287</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.006662008606174412</v>
+        <v>-0.002353796873090072</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.004600268964489202</v>
+        <v>-0.01212152264435616</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.002721354247991698</v>
+        <v>0.006950370182270598</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.021183542709932</v>
+        <v>0.04209905923953802</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.001891528479705529</v>
+        <v>0.07027302931752406</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01279605630331458</v>
+        <v>0.07538959071439934</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.02914493717491839</v>
+        <v>0.09737990002385154</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,25 +2365,25 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.00646705702208672</v>
+        <v>-0.06519405904416997</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.004254766081998416</v>
+        <v>-0.1036221327151773</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
         <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.008842136608880675</v>
+        <v>-0.04241719201057433</v>
       </c>
       <c r="CF4" t="n">
         <v>-0</v>
@@ -2392,52 +2392,52 @@
         <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.003656664493049632</v>
+        <v>0.002845902090864143</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.02431223590046886</v>
+        <v>0.06505154403546018</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.001889165091511889</v>
+        <v>-0.1040704937617431</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.007976712907845133</v>
+        <v>0.08087427056693047</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.007423918844361335</v>
+        <v>0.0437587442353984</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.006524673286280014</v>
+        <v>-0.04839172308457222</v>
       </c>
       <c r="CX4" t="n">
         <v>0</v>
@@ -2446,13 +2446,13 @@
         <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.004113090764874826</v>
+        <v>-0.004754709552484421</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0259473737194616</v>
+        <v>0.06082346818742058</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
         <v>0</v>
@@ -2461,22 +2461,22 @@
         <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.0115071602606346</v>
+        <v>-0.01960417706160444</v>
       </c>
       <c r="DG4" t="n">
         <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.01490431191527703</v>
+        <v>-0.03100171315222487</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.04330166262022572</v>
+        <v>0.01892771312810526</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
@@ -2485,28 +2485,28 @@
         <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.004148577184107919</v>
+        <v>-0.01770552854168653</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.008121536343683551</v>
+        <v>0.02910673750342943</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.00193228121266712</v>
+        <v>0.08951589615409841</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
@@ -2518,19 +2518,19 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.002527108708970274</v>
+        <v>-0.00347909460267912</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.009194774617788882</v>
+        <v>-0.02093529500500036</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.02084577538227626</v>
+        <v>-0.03871291937488223</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
@@ -2542,52 +2542,52 @@
         <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.002173243774021946</v>
+        <v>-0.05223128393447855</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.003930032738857992</v>
+        <v>-0.03261091786811723</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.01260477785563613</v>
+        <v>0.03480333104975204</v>
       </c>
       <c r="EL4" t="n">
         <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.001059538363532831</v>
+        <v>0.003031637441020463</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.005761741619455478</v>
+        <v>-0.0441650513897355</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.02885919399575161</v>
+        <v>0.0492110916658239</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
@@ -2596,10 +2596,10 @@
         <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.007071451334790081</v>
+        <v>-0.04981888760528227</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
@@ -2608,25 +2608,25 @@
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.00129655348315024</v>
+        <v>-0.01408533921513115</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.02560586054948842</v>
+        <v>0.05381370926058662</v>
       </c>
       <c r="FD4" t="n">
         <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.009628971536239277</v>
+        <v>-0.07092795019088584</v>
       </c>
       <c r="FI4" t="n">
         <v>0</v>
@@ -2635,10 +2635,10 @@
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.01652807382550421</v>
+        <v>0.01503424341543462</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.003638548315265669</v>
+        <v>-0.0221448681553416</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,25 +2647,25 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.001102977925613183</v>
+        <v>0.03414380935894204</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.01317953042564743</v>
+        <v>0.002474672424062624</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.01401387099279632</v>
+        <v>0.04920123820690302</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
@@ -2674,13 +2674,13 @@
         <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.01883095932802459</v>
+        <v>-0.00990107138770227</v>
       </c>
       <c r="GA4" t="n">
         <v>0</v>
@@ -2689,10 +2689,10 @@
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.008247301157067378</v>
+        <v>0.04835346849183468</v>
       </c>
       <c r="GE4" t="n">
         <v>0</v>
@@ -2701,27 +2701,27 @@
         <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.08448709830620459</v>
+        <v>0.1792632989284406</v>
       </c>
       <c r="C5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.02786977553366855</v>
+        <v>-0.06599792599585859</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0305102295231295</v>
+        <v>-0.04047478757385281</v>
       </c>
       <c r="F5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>-0</v>
@@ -2736,16 +2736,16 @@
         <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02947178552890657</v>
+        <v>0.1013112538678458</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.007447429405822174</v>
+        <v>0.02342521010426184</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.02883627110379305</v>
+        <v>-0.0348604908456948</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2760,19 +2760,19 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.042734425453061e-11</v>
+        <v>3.583051447179607e-11</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-8.811750641239269e-12</v>
+        <v>5.175439961242415e-12</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.005439004691367176</v>
+        <v>-0.002768529610030347</v>
       </c>
       <c r="X5" t="n">
         <v>-0</v>
@@ -2781,52 +2781,52 @@
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.004436310168589842</v>
+        <v>0.0006266311320576084</v>
       </c>
       <c r="AD5" t="n">
         <v>-0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.02252246465259293</v>
+        <v>-0.08458822910239887</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.04877508477370974</v>
+        <v>-0.07072261935277341</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.009100772465002053</v>
+        <v>0.09698390748479377</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.03607513824239714</v>
+        <v>-0.0114601638790719</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.05871639235244757</v>
+        <v>0.07883561958246234</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
@@ -2835,52 +2835,52 @@
         <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.2899931191746864</v>
+        <v>0.3070125330884234</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.05440847482512166</v>
+        <v>-0.139019825078348</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1626639365008442</v>
+        <v>-0.1623415816370824</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB5" t="n">
         <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.01541735200783675</v>
+        <v>-0.003261852880407696</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.02383828119269199</v>
+        <v>0.002478180132303887</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.0125802110389363</v>
+        <v>-0.003588380510446762</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2895,25 +2895,25 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.06892545366631524</v>
+        <v>-0.0108504051263354</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.02811442983746073</v>
+        <v>0.05899974047189726</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1211857235338337</v>
+        <v>0.09042300392528543</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,76 +2925,76 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.154586894499396</v>
+        <v>0.2309843920342081</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.03147257965239317</v>
+        <v>-0.09184427898330705</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.0203944431489949</v>
+        <v>-0.0123390509119493</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
         <v>-0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.0249251878051573</v>
+        <v>-0.1090762262205675</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.01212960627325187</v>
+        <v>0.08693087890619834</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.001455814260402229</v>
+        <v>0.0143199130701243</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
         <v>-0</v>
       </c>
       <c r="CK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL5" t="n">
         <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.01993856824918178</v>
+        <v>-0.1273245197949835</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.03477290511058178</v>
+        <v>0.02155428560962999</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.1415269911662926</v>
+        <v>0.03266062877906627</v>
       </c>
       <c r="CR5" t="n">
         <v>0</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
         <v>-0</v>
@@ -3006,19 +3006,19 @@
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.01287838832630447</v>
+        <v>-0.120541919938229</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.02395415254219926</v>
+        <v>0.09424499725419559</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.01973920793089495</v>
+        <v>0.02055238042305829</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
         <v>0</v>
@@ -3030,25 +3030,25 @@
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.001479911612681613</v>
+        <v>-0.006656995666993146</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.01532916273055872</v>
+        <v>0.04017802366671934</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.02793624540504774</v>
+        <v>-0.04528049230675816</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
         <v>0</v>
@@ -3060,76 +3060,76 @@
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.07140241514980719</v>
+        <v>-0.05906971903632968</v>
       </c>
       <c r="DP5" t="n">
         <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.0007304147547142439</v>
+        <v>0.01374764136355673</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.01195630204819023</v>
+        <v>-0.06070149095036304</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.001916730661515114</v>
+        <v>0.05888383762261446</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.0380778680897892</v>
+        <v>0.05489247016277397</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.02040796799145321</v>
+        <v>-0.0318441212454026</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
         <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.0280710494967211</v>
+        <v>-0.05795631330156423</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.01440671169675183</v>
+        <v>0.09933354918426889</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.05314423097666537</v>
+        <v>0.03449599101007193</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
         <v>-0</v>
@@ -3141,22 +3141,22 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.02768072988059273</v>
+        <v>-0.06466939570099636</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.03212079558242339</v>
+        <v>0.0637119549569094</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.02864617831363411</v>
+        <v>-0.049161944941338</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>-0</v>
@@ -3165,25 +3165,25 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.01901962561049784</v>
+        <v>-0.1321879592513165</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.02658628512584578</v>
+        <v>0.107353588477369</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.01545247591283949</v>
+        <v>0.009413386044630155</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
@@ -3192,76 +3192,76 @@
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.04992584196316089</v>
+        <v>-0.06731940448832742</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.0453617353156317</v>
+        <v>-0.03906527655567107</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.02226105356152701</v>
+        <v>0.06952793151159202</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.09021693348759388</v>
+        <v>0.03934317771206858</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.05084960221248787</v>
+        <v>0.1115512409047754</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.06344617547041068</v>
+        <v>-0.09451632406430974</v>
       </c>
       <c r="FU5" t="n">
         <v>0</v>
       </c>
       <c r="FV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.01243436855925006</v>
+        <v>-0.09193225340113872</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.01599230979825867</v>
+        <v>0.03659353195258691</v>
       </c>
       <c r="GC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
@@ -3275,25 +3275,25 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01664923530466404</v>
+        <v>0.02822148301017316</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.01045258823172225</v>
+        <v>0.00971682169302117</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.002477909982477682</v>
+        <v>-0.006312844439299586</v>
       </c>
       <c r="G6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -3305,22 +3305,22 @@
         <v>-0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004127545552203832</v>
+        <v>0.03330428184646565</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.008719310704894423</v>
+        <v>0.003308183188614977</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.001400011342580543</v>
+        <v>-0.002931996742086458</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -3332,52 +3332,52 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.381491629216613e-05</v>
+        <v>-0.0009324453990341448</v>
       </c>
       <c r="U6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-5.227018458916527e-12</v>
+        <v>-1.36351117233671e-11</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.003435149859108066</v>
+        <v>3.864344945975604e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.01241463141599104</v>
+        <v>-0.01910955964570647</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.01134507365079849</v>
+        <v>-0.04355841627853808</v>
       </c>
       <c r="AG6" t="n">
-        <v>-9.123156602400261e-05</v>
+        <v>-0.01751883960254777</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
@@ -3386,22 +3386,22 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.005186977387503058</v>
+        <v>0.01381751309967641</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.01906639628305302</v>
+        <v>-0.006415116998292692</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.005027499552368327</v>
+        <v>-0.02142645886700914</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
         <v>-0</v>
@@ -3410,22 +3410,22 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.03768763401701408</v>
+        <v>0.09536990420180071</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.012373201578964</v>
+        <v>-0.01468726470838176</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.006177742337163695</v>
+        <v>-0.01623710569190458</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3437,25 +3437,25 @@
         <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.002262475740561792</v>
+        <v>-0.004559971807533743</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.005056359545989117</v>
+        <v>-0.004988229449101703</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.001994314521051327</v>
+        <v>0.009063439902154814</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
         <v>0</v>
@@ -3464,37 +3464,37 @@
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.02341681351247221</v>
+        <v>0.01150030705735437</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.01040078194045738</v>
+        <v>0.03866388632335679</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.0105759473226288</v>
+        <v>0.03203446062869997</v>
       </c>
       <c r="BR6" t="n">
         <v>-0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.01752375341390967</v>
+        <v>0.03764753040551198</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.008035965353252936</v>
+        <v>-0.002039528079909779</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.01902415782307544</v>
+        <v>-0.02923189462565513</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3521,22 +3521,22 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.0009396198720446748</v>
+        <v>-0.01142532770542942</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.001265102301200815</v>
+        <v>0.001286489763983061</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.00516011414307044</v>
+        <v>0.02046650931693459</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -3545,52 +3545,52 @@
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.003012793553904942</v>
+        <v>-0.02608579669879785</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.0001611915406061993</v>
+        <v>0.04050225526445645</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.01549277932784901</v>
+        <v>0.02014858431043228</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
         <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.004370593022699762</v>
+        <v>-0.01353103421843109</v>
       </c>
       <c r="CX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.002097486081708762</v>
+        <v>-0.0004538179254309182</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.005710518806811176</v>
+        <v>0.0179653285899996</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
         <v>0</v>
@@ -3599,22 +3599,22 @@
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.001987215268027764</v>
+        <v>-0.01818900024910615</v>
       </c>
       <c r="DG6" t="n">
         <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>8.67059149038475e-05</v>
+        <v>-0.000901091578240512</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.01237432096763877</v>
+        <v>-0.005518683132805723</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,58 +3623,58 @@
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.003830298588681193</v>
+        <v>-0.01612920230728051</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01028071538605144</v>
+        <v>0.007007096556723299</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.00497338858561754</v>
+        <v>0.02969104207855926</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.01389042070268526</v>
+        <v>-0.008021970681250207</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.01077654224419827</v>
+        <v>0.00337619668351938</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.001274202522548146</v>
+        <v>0.02614651048654467</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
@@ -3683,46 +3683,46 @@
         <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.002312629102065329</v>
+        <v>-0.0125580285559567</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.003910800276870598</v>
+        <v>-0.01433101115931057</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.003350185419914363</v>
+        <v>0.001023454066969717</v>
       </c>
       <c r="EL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.003265828115631627</v>
+        <v>0.003248731948691825</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.009237966621120332</v>
+        <v>-0.00383940805707055</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.03245001386739178</v>
+        <v>0.008375445249409062</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
@@ -3731,52 +3731,52 @@
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.005896815329702098</v>
+        <v>-0.01594140051838182</v>
       </c>
       <c r="EZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA6" t="n">
         <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.002632832250342733</v>
+        <v>-0.006117581569139427</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.00748874728956123</v>
+        <v>0.01405891358465753</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF6" t="n">
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.01177160726450066</v>
+        <v>-0.01733908339124667</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.01350726249386292</v>
+        <v>0.01705065630495674</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.0238211427868699</v>
+        <v>0.005004581578143138</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.006546759746832906</v>
+        <v>0.01056089207462325</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
@@ -3800,10 +3800,10 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.001647881589228021</v>
+        <v>0.006675739452162158</v>
       </c>
       <c r="FU6" t="n">
-        <v>-0.0006343720858502663</v>
+        <v>-0.03171368309356283</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
@@ -3812,31 +3812,31 @@
         <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.01405900208865225</v>
+        <v>0.00418704314735095</v>
       </c>
       <c r="GA6" t="n">
         <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.006142392214902499</v>
+        <v>0.008474098012037294</v>
       </c>
       <c r="GE6" t="n">
         <v>0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.07922185897965527</v>
+        <v>0.04447456241560004</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.009568064064697065</v>
+        <v>-0.01633963234827682</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,22 +3868,22 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.004516347136445872</v>
+        <v>-0.00128204601680669</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02896707786701479</v>
+        <v>0.0474755550615052</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.03698409720773339</v>
+        <v>-0.01492842921554724</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         <v>-0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.001885510811597013</v>
+        <v>-0.0002586770533533154</v>
       </c>
       <c r="S7" t="n">
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002757484100180435</v>
+        <v>-0.001470593295039007</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
@@ -3910,34 +3910,34 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.001090815487736433</v>
+        <v>-0.002578123113928714</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0005160410835590934</v>
+        <v>0.000450188918958079</v>
       </c>
       <c r="AB7" t="n">
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.03512531007090526</v>
+        <v>-0.01646757697993833</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.02738385431066692</v>
+        <v>-0.02318283739543439</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -3946,16 +3946,16 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01263768000576627</v>
+        <v>-5.670802835179089e-05</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.02442944307325537</v>
+        <v>0.02391483464439334</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,37 +3964,37 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.02288364457710829</v>
+        <v>-0.007830062473386799</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.0142907337844646</v>
+        <v>-0.008449794391440661</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1662560559676156</v>
+        <v>0.09069458038694041</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.06513288123626994</v>
+        <v>-0.02241129973239056</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4003,13 +4003,13 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.004537500812004287</v>
+        <v>0.009797470737476242</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.005701427748892611</v>
+        <v>-0.00346812895716898</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,25 +4018,25 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.02157487898423979</v>
+        <v>-0.007109179838770867</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.02139353320428345</v>
+        <v>0.01137221323222175</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.01577329106320983</v>
+        <v>0.01307272226117364</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
@@ -4045,52 +4045,52 @@
         <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.07328775648029445</v>
+        <v>0.03200181212551792</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.02692819190524353</v>
+        <v>0.01066066581775328</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.08272539266660328</v>
+        <v>0.05277298110401246</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.01153594911989237</v>
+        <v>-0.01838181616277979</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.008760847297346051</v>
+        <v>-0.01368122303622788</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.01924771929669158</v>
+        <v>-0.02088944526462655</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
@@ -4099,10 +4099,10 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.0005614518250307024</v>
+        <v>0.006309172057940526</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
@@ -4111,25 +4111,25 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.02535101553817352</v>
+        <v>0.009325117656581972</v>
       </c>
       <c r="CM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.02138404467407852</v>
+        <v>-0.031970182643326</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
         <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.01649618257967604</v>
+        <v>0.008894133372832281</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,13 +4138,13 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.005182698189409238</v>
+        <v>0.02056456654782044</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.01535094361568996</v>
+        <v>-0.02211457072350442</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
@@ -4153,34 +4153,34 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.004839264423676924</v>
+        <v>0.00396759781354036</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.02494151222536031</v>
+        <v>0.008717561711871265</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.06712681243915618</v>
+        <v>-0.0118146842152844</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.02972886974855416</v>
+        <v>-0.008423827115044323</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
@@ -4192,52 +4192,52 @@
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.002749001572195376</v>
+        <v>-0.008561900105861581</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.003718467693625823</v>
+        <v>-0.01559501016341675</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.006844606647754456</v>
+        <v>0.003791572314905713</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
         <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0.002809965376044405</v>
+        <v>-0.02390010800848033</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.002574257602074628</v>
+        <v>0.01059276347422734</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
         <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.01768638723281177</v>
+        <v>-0.009524538069059686</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
@@ -4246,40 +4246,40 @@
         <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>-0.01270861034296726</v>
+        <v>0.002005612941475804</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.002448434508034231</v>
+        <v>-0.01378564699553455</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.02338987615849451</v>
+        <v>-0.003003080127459122</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.02629705342984468</v>
+        <v>0.003278837046040156</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.03449304003223867</v>
+        <v>-0.003865453042709505</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
@@ -4288,25 +4288,25 @@
         <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.001294588907499899</v>
+        <v>-0.003258797957880477</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.009414040387965695</v>
+        <v>0.00705418172467024</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.02605549440651283</v>
+        <v>-0.02492854851603489</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,7 +4315,7 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.005844626312338378</v>
+        <v>-0.000476081838525441</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
@@ -4327,22 +4327,22 @@
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.01511886310422681</v>
+        <v>0.009137077863824852</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.02645727773213055</v>
+        <v>-0.01436585418436683</v>
       </c>
       <c r="FI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.02359112244592703</v>
+        <v>0.002963281524501794</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
@@ -4351,16 +4351,16 @@
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.01308353585084712</v>
+        <v>0.04059846726735821</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.04427098796880272</v>
+        <v>0.008919243316668705</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
@@ -4369,7 +4369,7 @@
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.005971297432784496</v>
+        <v>-0.01633811995091359</v>
       </c>
       <c r="FU7" t="n">
         <v>0</v>
@@ -4378,19 +4378,19 @@
         <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.0004243337770675755</v>
+        <v>0.0008777176177734854</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.03344965375194718</v>
+        <v>-0.008333494156679385</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.02902152564144799</v>
+        <v>0.005205309732925113</v>
       </c>
     </row>
     <row r="8">
@@ -4982,46 +4982,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2815015323028037</v>
+        <v>0.1448653406934446</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1208522464173851</v>
+        <v>-0.09050642772147345</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.05840785980081597</v>
+        <v>-0.04762602003502105</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1505880726912145</v>
+        <v>0.1197812251368858</v>
       </c>
       <c r="L9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.07882796190891085</v>
+        <v>-0.09030416694270176</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.06612350769493712</v>
+        <v>-0.07963588315919549</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5036,28 +5036,28 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.02370641419775992</v>
+        <v>0.02704946679454651</v>
       </c>
       <c r="U9" t="n">
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.003610685294156945</v>
+        <v>-0.005240814026905202</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.006445007706906422</v>
+        <v>-0.01214703215433605</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -5066,19 +5066,19 @@
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.09619631328945855</v>
+        <v>0.001814376442448044</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.03120319462958932</v>
+        <v>-0.06497864864809834</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.02725571145464951</v>
+        <v>-0.1150567674005206</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
         <v>-0</v>
@@ -5087,22 +5087,22 @@
         <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.008445319714667152</v>
+        <v>0.1588902048889499</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.03003089550876374</v>
+        <v>-0.08558448758149666</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.1190867863840156</v>
+        <v>0.04516003122852094</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5120,19 +5120,19 @@
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.4430741806979165</v>
+        <v>0.2687995805099087</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.0198739816318064</v>
+        <v>-0.06275893980498976</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.132380198465229</v>
+        <v>-0.2765347036645754</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -5144,19 +5144,19 @@
         <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.02088199612367187</v>
+        <v>-0.03820101119793233</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.02029056813375596</v>
+        <v>-0.00375279959403441</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.07487967071623949</v>
+        <v>0.003924329494016041</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,19 +5174,19 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.1540741063666666</v>
+        <v>0.04609675576622783</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.02163675467499574</v>
+        <v>0.02854006354520243</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1090520085015167</v>
+        <v>0.04572550961117841</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
         <v>-0</v>
@@ -5201,19 +5201,19 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.2288939287119959</v>
+        <v>0.2235702450572448</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0.04095236715406394</v>
+        <v>-0.1930134432267097</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.01192204492861598</v>
+        <v>-0.06936909134021703</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
@@ -5228,25 +5228,25 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.06743275022342679</v>
+        <v>-0.06845714062820506</v>
       </c>
       <c r="CF9" t="n">
         <v>0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.009583424915312498</v>
+        <v>0.1090181569163802</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.01465727083479497</v>
+        <v>0.03415990134168976</v>
       </c>
       <c r="CI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
         <v>-0</v>
@@ -5255,76 +5255,76 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.07503466819427111</v>
+        <v>-0.1168609662767022</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.1211022376441834</v>
+        <v>0.2657339762761787</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.1087916105036191</v>
+        <v>0.1209546030237584</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.04444504882168809</v>
+        <v>-0.05395829920881032</v>
       </c>
       <c r="CX9" t="n">
         <v>-0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0360654944971033</v>
+        <v>0.1226822242566384</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.004708730200157574</v>
+        <v>0.04725035555084115</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
         <v>-0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.01505040571861022</v>
+        <v>-0.006346084729805677</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.04801469908775666</v>
+        <v>0.01529403059661255</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.02299946743385808</v>
+        <v>-0.0632466661418787</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
@@ -5336,154 +5336,154 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.07799512042234789</v>
+        <v>-0.0745184415802491</v>
       </c>
       <c r="DP9" t="n">
         <v>0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.02435048511521843</v>
+        <v>0.05867219678983252</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.009302787974615189</v>
+        <v>0.005794533961279938</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.03168019952069409</v>
+        <v>0.0371209197394515</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.04248527632422641</v>
+        <v>0.0406481383422866</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.002436373935883997</v>
+        <v>-0.06131583023826693</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
         <v>0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.01634857192723618</v>
+        <v>0.01342956189122112</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.06288372751455945</v>
+        <v>0.08192688216667893</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.04916425981173941</v>
+        <v>0.03768395881497294</v>
       </c>
       <c r="EK9" t="n">
         <v>-0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.06838926736353844</v>
+        <v>-0.05513346761439614</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.05901818408101457</v>
+        <v>-0.1147671333277322</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.01268305549595014</v>
+        <v>0.005425690209789459</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX9" t="n">
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.05539113821086633</v>
+        <v>-0.07418066202155051</v>
       </c>
       <c r="EZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.02657982519805805</v>
+        <v>0.132677407016655</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.009019296767391256</v>
+        <v>0.02768241262600696</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.05297491708190308</v>
+        <v>-0.02011879946787459</v>
       </c>
       <c r="FI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.04857848612537258</v>
+        <v>0.02860538023515257</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.01749975006793934</v>
+        <v>-0.02904257197731498</v>
       </c>
       <c r="FL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
@@ -5492,58 +5492,58 @@
         <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.03221926591635039</v>
+        <v>0.0218575464383613</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.02324279929384894</v>
+        <v>0.09590809207888946</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.09921848001933811</v>
+        <v>-0.171970459770996</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.02588865039475632</v>
+        <v>-0.02213380313627245</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.02298568282209811</v>
+        <v>0.04053010215258065</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>0</v>
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2470845184349121</v>
+        <v>0.1452840372433351</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1032366070099718</v>
+        <v>-0.131331195759352</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0957371087706937</v>
+        <v>-0.08170226152581059</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5572,7 +5572,7 @@
         <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>8.418312676320214e-12</v>
+        <v>1.593442048875061e-11</v>
       </c>
       <c r="I10" t="n">
         <v>-0</v>
@@ -5581,16 +5581,16 @@
         <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1325711804502957</v>
+        <v>0.1029174336500599</v>
       </c>
       <c r="L10" t="n">
         <v>-0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.06761988976674783</v>
+        <v>-0.1178524777008875</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1422226303718421</v>
+        <v>-0.1007321061759059</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5599,52 +5599,52 @@
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.003314780231591662</v>
+        <v>0.001804104753710435</v>
       </c>
       <c r="R10" t="n">
         <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.06317859121621232</v>
+        <v>0.04271602773450917</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.01303335741866291</v>
+        <v>-0.02644540698902321</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0015459476700098</v>
+        <v>-0.0492548089247023</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.001819389485213783</v>
+        <v>0.0142837973153775</v>
       </c>
       <c r="AA10" t="n">
         <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.07161296761543931</v>
+        <v>-0.05520200911852526</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.08395704982368586</v>
+        <v>-0.04811984196864123</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.0278496678587558</v>
+        <v>-0.1563189624103223</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -5653,52 +5653,52 @@
         <v>-0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.01370889197630573</v>
+        <v>0.02502052328878236</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.01904653787671291</v>
+        <v>0.1255922227165079</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.05667754884537556</v>
+        <v>-0.01035707070278512</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.08915760464658547</v>
+        <v>0.02911242824417222</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.0002112893193432413</v>
+        <v>-0.002303002411648067</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT10" t="n">
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.4660783052485977</v>
+        <v>0.2372770417049324</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0007710893488538321</v>
+        <v>-0.05098802671038242</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1727315910402573</v>
+        <v>-0.2707854512229036</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
@@ -5707,7 +5707,7 @@
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0473186164558993</v>
+        <v>-0.04658341969222341</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.01179936853734211</v>
+        <v>-0.0329417998654488</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.03159502942562394</v>
+        <v>-0.05221639786567711</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.1622562764638793</v>
+        <v>-0.01373822294826299</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,34 +5734,34 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-0.00288754729847395</v>
+        <v>-0.01438830625033437</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.1441893567899667</v>
+        <v>0.0519688777576907</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.1268418533182775</v>
+        <v>0.09349283003940216</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1270343105504727</v>
+        <v>0.03777130925018957</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.04196688304884907</v>
+        <v>0.006347008219980432</v>
       </c>
       <c r="BT10" t="n">
         <v>-0</v>
@@ -5770,52 +5770,52 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.227676970697377</v>
+        <v>0.198185208771163</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.02744911718257402</v>
+        <v>-0.1150884523977013</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.03179656389712266</v>
+        <v>-0.1583601133427264</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.001464439160883281</v>
+        <v>-0.07014002896614492</v>
       </c>
       <c r="CC10" t="n">
         <v>-0</v>
       </c>
       <c r="CD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.07016588562524181</v>
+        <v>-0.03911206513455348</v>
       </c>
       <c r="CF10" t="n">
         <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.02402740650066615</v>
+        <v>0.09560603048218795</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.002203342236885705</v>
+        <v>0.04014014007985297</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.006681223797264205</v>
+        <v>-0.01769256314661922</v>
       </c>
       <c r="CL10" t="n">
         <v>-0</v>
@@ -5824,43 +5824,43 @@
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.07638307740903713</v>
+        <v>-0.02205667761502917</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.1114783571240855</v>
+        <v>0.1200299083980905</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.01474261611556455</v>
+        <v>0.2137799472192194</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.06276036132058843</v>
+        <v>0.05697424299601278</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.04222639997829995</v>
+        <v>-0.04092731550665441</v>
       </c>
       <c r="CX10" t="n">
         <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.0460303735604865</v>
+        <v>0.1150981871087791</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.007035805461602548</v>
+        <v>0.05643733932405119</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5869,52 +5869,52 @@
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.008951181726513021</v>
+        <v>-0.01210198782491596</v>
       </c>
       <c r="DD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.06240458467698688</v>
+        <v>-0.04244064246546284</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.0340490407089142</v>
+        <v>0.03588469607416355</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.001977788978849075</v>
+        <v>-0.00751516900995579</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
         <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.001107704777725401</v>
+        <v>-0.01995038232092895</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.08825651888727057</v>
+        <v>-0.04901289244141144</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.02550367924007988</v>
+        <v>0.03970824051064364</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.04774729586677496</v>
+        <v>-0.08400867105764155</v>
       </c>
       <c r="DS10" t="n">
         <v>-0</v>
@@ -5923,133 +5923,133 @@
         <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>-0.03592336004037908</v>
+        <v>0.09511612937445459</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.01592359962308398</v>
+        <v>0.04985045906308443</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.03336998938484566</v>
+        <v>0.07570177401367424</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.03449827806887938</v>
+        <v>-0.09672294108565842</v>
       </c>
       <c r="EB10" t="n">
         <v>0</v>
       </c>
       <c r="EC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0.02863860063263021</v>
+        <v>0.08202653999762531</v>
       </c>
       <c r="EE10" t="n">
         <v>0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.02351870879856304</v>
+        <v>0.02418496504588205</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.07332782434434365</v>
+        <v>0.06867151559210341</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.03159212830118156</v>
+        <v>0.01461554072005258</v>
       </c>
       <c r="EK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL10" t="n">
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.04571388947874493</v>
+        <v>-0.02735959858559283</v>
       </c>
       <c r="EN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO10" t="n">
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.08891431696905695</v>
+        <v>-0.01555104294840053</v>
       </c>
       <c r="EQ10" t="n">
         <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.08898723232583954</v>
+        <v>0.1108334121736521</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.03700315619288005</v>
+        <v>-0.01762669003671506</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.01282251699825968</v>
+        <v>-0.002073631917067486</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.05356413819858893</v>
+        <v>-0.05781110574887327</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.03990485758713448</v>
+        <v>0.1197815128554732</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.02078275295389396</v>
+        <v>0.04512406089039162</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.005060624634846344</v>
+        <v>-0.007209195275849487</v>
       </c>
       <c r="FF10" t="n">
         <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.07147286892967199</v>
+        <v>-0.002048978872477619</v>
       </c>
       <c r="FI10" t="n">
         <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0.0335940618063249</v>
+        <v>-0.01609027816547187</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.01550435550165679</v>
+        <v>0.09206416623805666</v>
       </c>
       <c r="FL10" t="n">
         <v>-0</v>
@@ -6058,61 +6058,61 @@
         <v>-0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0.004328188445603767</v>
+        <v>-0.03723280376314283</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.09869269903919436</v>
+        <v>-0.004913816735995803</v>
       </c>
       <c r="FR10" t="n">
         <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.06003857865542035</v>
+        <v>0.1313995879897296</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.0642012877459487</v>
+        <v>-0.1984325885447277</v>
       </c>
       <c r="FU10" t="n">
         <v>0</v>
       </c>
       <c r="FV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.01558547125309226</v>
+        <v>-0.04406490576629499</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.09723489434697646</v>
+        <v>-0.01883374555667174</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.03408020382976761</v>
+        <v>0.03479123828609451</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.02997556362139621</v>
+        <v>-0.04218110078719987</v>
       </c>
       <c r="GG10" t="n">
         <v>-0</v>
@@ -6123,25 +6123,25 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.08386019570165759</v>
+        <v>0.2903087469646763</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
         <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.06522150719378753</v>
+        <v>-0.007358998889636519</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.05546696572897549</v>
+        <v>-0.1873672758151216</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.03939665779855735</v>
+        <v>0.3121133399166205</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,13 +6159,13 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.05880161780247598</v>
+        <v>-0.06808146099008384</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.04269197164562</v>
+        <v>-0.1329137607608467</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -6174,10 +6174,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01193767360639306</v>
+        <v>0.06400567504647325</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -6186,37 +6186,37 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.003887891417489284</v>
+        <v>-0.05822997225440397</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01631350122578821</v>
+        <v>0.01023146732339812</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.02576771826607821</v>
+        <v>-0.03807174186872388</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0161230657898242</v>
+        <v>-0.226736191891142</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.01828038971144951</v>
+        <v>0.03824512499772518</v>
       </c>
       <c r="AH11" t="n">
         <v>-0</v>
@@ -6231,7 +6231,7 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.01862952327857872</v>
+        <v>0.09588278893474857</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,25 +6240,25 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.02079485937495316</v>
+        <v>-0.04716896418132886</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.006305069628821995</v>
+        <v>-0.03675589192534068</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1148501591063746</v>
+        <v>0.5238305471964579</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -6267,67 +6267,67 @@
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.01982105413432997</v>
+        <v>-0.2157211437801604</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.01331131022273548</v>
+        <v>-0.06274504746608825</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.01886609089848843</v>
+        <v>-0.04013099828935125</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.04163644946467512</v>
+        <v>-0.01760131412817515</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.03038570218869392</v>
+        <v>-0.07068688383811574</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.06282053611353099</v>
+        <v>0.1366476027720558</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.03549362494843274</v>
+        <v>0.1422197394713917</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.01398241373608709</v>
+        <v>0.09292274485959325</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>0</v>
@@ -6339,7 +6339,7 @@
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.04480032023902552</v>
+        <v>0.3501656362895281</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,40 +6348,40 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.01648018933317369</v>
+        <v>-0.07197471294937022</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.01221034380930878</v>
+        <v>-0.05782996739983203</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.01693604172628734</v>
+        <v>-0.1179268084787689</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.01310989270599581</v>
+        <v>-0.0004026542133790641</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.01598140425278118</v>
+        <v>0.07975239114852251</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
@@ -6393,61 +6393,61 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.01797904499006639</v>
+        <v>-0.2195290878890573</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
         <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.012813331326182</v>
+        <v>0.07522625300375177</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.009958092523241905</v>
+        <v>0.008187858286100379</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU11" t="n">
         <v>0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.006167419776663866</v>
+        <v>-0.1017381949368624</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.01253674291060891</v>
+        <v>-0.01586173200886005</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.01735817807204967</v>
+        <v>0.08475563477054694</v>
       </c>
       <c r="DB11" t="n">
         <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.009366013012976926</v>
+        <v>-0.1007300711447598</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
@@ -6456,37 +6456,37 @@
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.009641696523764063</v>
+        <v>-0.1333662955229793</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.00945395233475476</v>
+        <v>-0.001551666111173646</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.0182402524730501</v>
+        <v>-0.06402121745793986</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.02134504797240114</v>
+        <v>-0.03712935969047027</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.0285223022849072</v>
+        <v>-0.02113825255085331</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
@@ -6501,106 +6501,106 @@
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.005108023396178977</v>
+        <v>0.07117222589704097</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.02456951038313874</v>
+        <v>0.001278538770799062</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.00830155218310508</v>
+        <v>0.04988009658823794</v>
       </c>
       <c r="EC11" t="n">
         <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.003666131265358069</v>
+        <v>0.01199008427691833</v>
       </c>
       <c r="EH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI11" t="n">
         <v>0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.005048487493100426</v>
+        <v>-0.05901820539712842</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.004121900642494842</v>
+        <v>0.06683154386318631</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.01099702206278394</v>
+        <v>-0.007338842621273805</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.005869001025938502</v>
+        <v>-0.1377539053533816</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.0200487587167411</v>
+        <v>0.0536317657316782</v>
       </c>
       <c r="EU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.003110707809250975</v>
+        <v>-0.1331196119999002</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.01186076008728186</v>
+        <v>-0.03438399298859528</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.02027571353337713</v>
+        <v>0.06310180625688915</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF11" t="n">
         <v>-0</v>
@@ -6609,25 +6609,25 @@
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.01868431551209963</v>
+        <v>-0.1212817869760008</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.03370005626679827</v>
+        <v>0.1398729171198509</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.01019727416974537</v>
+        <v>0.04211160910336433</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
@@ -6636,7 +6636,7 @@
         <v>0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.001942208933395002</v>
+        <v>0.06850690239190561</v>
       </c>
       <c r="FR11" t="n">
         <v>0</v>
@@ -6645,25 +6645,25 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.00240353946153704</v>
+        <v>-0.0941062091000867</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.02272525983892771</v>
+        <v>-0.01870372393844412</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.03485333017983137</v>
+        <v>-0.06172339587495541</v>
       </c>
       <c r="GA11" t="n">
         <v>0</v>
@@ -6675,10 +6675,10 @@
         <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.006044718825042113</v>
+        <v>0.1025432731369546</v>
       </c>
       <c r="GE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF11" t="n">
         <v>-0</v>
@@ -6692,16 +6692,16 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1831009557201636</v>
+        <v>0.3034013118400758</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1060593485531727</v>
+        <v>-0.1550795785167024</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.04489676532069157</v>
+        <v>-0.01052999712905831</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -6716,136 +6716,136 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1063697911766365</v>
+        <v>0.2745900187726399</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.07345940053961347</v>
+        <v>-0.1380242402973058</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0497979654738445</v>
+        <v>-0.03563158173978188</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12" t="n">
         <v>-0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.03631085528481948</v>
+        <v>0.05186083337986206</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0061625726913397</v>
+        <v>-0.01346012167590277</v>
       </c>
       <c r="W12" t="n">
-        <v>0.025658039445574</v>
+        <v>-0.03457576652352067</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.09995227882709326</v>
+        <v>-0.0753946020854333</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.00556558247609383</v>
+        <v>-0.1137677298688956</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.03051585414793436</v>
+        <v>-0.06083723452895615</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.01917841603217064</v>
+        <v>0.09302259395743348</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.04368357595067415</v>
+        <v>-0.08604038224767276</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.06552836399036192</v>
+        <v>0.06560576321035769</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.3071109363747874</v>
+        <v>0.2599302266924339</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.002568156944245914</v>
+        <v>-0.113417298593112</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.1126450766136668</v>
+        <v>-0.1442633514659499</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
@@ -6854,16 +6854,16 @@
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.03181312517018058</v>
+        <v>0.008936722213759837</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.0261595172612914</v>
+        <v>-0.01076551561463772</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.08946005205770644</v>
+        <v>-0.003368136329892062</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,22 +6881,22 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.08055173332725529</v>
+        <v>-0.01302533702311111</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.04695688553872427</v>
+        <v>0.04048784403292859</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.0841318064231478</v>
+        <v>0.06916086672209069</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,25 +6908,25 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1507095830427172</v>
+        <v>0.2236960289870098</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.008083346531984684</v>
+        <v>-0.1018662339528547</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.04696234564514888</v>
+        <v>-0.02729463824234575</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
@@ -6935,19 +6935,19 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.04418183871991287</v>
+        <v>-0.1000833519216743</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>9.967608113416701e-05</v>
+        <v>0.1077657173100514</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.009148786739063247</v>
+        <v>-0.005854205689347341</v>
       </c>
       <c r="CI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ12" t="n">
         <v>-0</v>
@@ -6956,25 +6956,25 @@
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.02506748711447086</v>
+        <v>-0.07848923380455414</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.1174033061737398</v>
+        <v>0.1591920343187784</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.06983487472822746</v>
+        <v>0.02529583754122192</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6983,25 +6983,25 @@
         <v>-0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.02073680527128681</v>
+        <v>-0.09888524777555355</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.01725944506904914</v>
+        <v>0.1101233800209312</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.006105277870848949</v>
+        <v>0.002996084516745566</v>
       </c>
       <c r="DA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB12" t="n">
         <v>0</v>
@@ -7013,25 +7013,25 @@
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.001392780370202035</v>
+        <v>-0.1045726590604122</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.01666638481845247</v>
+        <v>0.01379061384094586</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.04025226264025477</v>
+        <v>-0.05026553030402559</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.04113664260661035</v>
+        <v>-0.07513135248526304</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0.007959020577800201</v>
+        <v>0.04608449436644046</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.02175367007617956</v>
+        <v>-0.008334614167847976</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
@@ -7067,79 +7067,79 @@
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.02058913822229661</v>
+        <v>0.004730871723100647</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.03595430473830787</v>
+        <v>-0.05595698297080601</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.006985418092378048</v>
+        <v>0.07116805258442153</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.01229827672938916</v>
+        <v>-0.05231458157210049</v>
       </c>
       <c r="EH12" t="n">
         <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.05023974831471428</v>
+        <v>0.07535085573625097</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.03407643361968344</v>
+        <v>0.03811383820901557</v>
       </c>
       <c r="EK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.03548369634189817</v>
+        <v>-0.03000079620669521</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.01194544256795099</v>
+        <v>0.06201840772464287</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.04807715361840442</v>
+        <v>-0.05025517794660409</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
@@ -7151,43 +7151,43 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.02885028174773058</v>
+        <v>-0.1134726908712005</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.01348713560515322</v>
+        <v>0.1267665245207414</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.003392347106282008</v>
+        <v>-0.0140135287749086</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
         <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.03008174869901151</v>
+        <v>-0.1093543266030141</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.03650844370813016</v>
+        <v>0.06912700111066354</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.02182824329361085</v>
+        <v>0.04788402408071511</v>
       </c>
       <c r="FL12" t="n">
         <v>0</v>
@@ -7196,28 +7196,28 @@
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.02837930425888821</v>
+        <v>0.0005928998662473312</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.02054164347519434</v>
+        <v>0.1145687898524336</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.06486808067495703</v>
+        <v>-0.05025009551588328</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
         <v>-0</v>
@@ -7226,31 +7226,31 @@
         <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.01296884947915551</v>
+        <v>-0.09466546004618347</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.04154562120512977</v>
+        <v>0.059786325013222</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
         <v>-0</v>
@@ -7258,22 +7258,22 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.3268034408455837</v>
+        <v>0.3973961137151564</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1058932470532249</v>
+        <v>0.02031697331490366</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2855569954863247</v>
+        <v>-0.3819732660629109</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7285,28 +7285,28 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2168084777427361</v>
+        <v>0.5106730628170991</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.08379488651862908</v>
+        <v>-0.06364873935579982</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2464841909373904</v>
+        <v>-0.3326021336590755</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7315,25 +7315,25 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.05956283581291213</v>
+        <v>0.132690170828735</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.001225833401078912</v>
+        <v>-0.1743199011573838</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01151444811975929</v>
+        <v>-0.03102785912536825</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -7342,19 +7342,19 @@
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.06310823751596506</v>
+        <v>-0.08564617503304743</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.06959444996247496</v>
+        <v>-0.4096881630404358</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.002186028697061561</v>
+        <v>-0.2449918696917483</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7363,28 +7363,28 @@
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.06614810857290319</v>
+        <v>0.1208022585903044</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.01603999414141288</v>
+        <v>0.02210451858709279</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.04434495428115299</v>
+        <v>-0.2006171332824782</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7393,109 +7393,109 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.3448998081073988</v>
+        <v>0.9734512936879771</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.03208987599191472</v>
+        <v>-0.2171429561558367</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.15230732543358</v>
+        <v>-0.1640434988076229</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.06409305123801945</v>
+        <v>-0.1519333862808784</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.08951310473147098</v>
+        <v>-0.1777542983028651</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.09428319918120509</v>
+        <v>-0.2094236171958231</v>
       </c>
       <c r="BI13" t="n">
         <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1198757440524535</v>
+        <v>0.1311459064835728</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.06440652925772231</v>
+        <v>0.1280284120157293</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.028985648156144</v>
+        <v>0.0559206754544701</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.1552988194534446</v>
+        <v>0.493229797631083</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.04696480134000203</v>
+        <v>-0.1790752056128389</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.0904079849604541</v>
+        <v>-0.272308940417327</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
         <v>0</v>
@@ -7504,46 +7504,46 @@
         <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.07441968184134365</v>
+        <v>-0.1737160891507045</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.00928170907382255</v>
+        <v>0.04779930269577396</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.07309898408206154</v>
+        <v>0.1819416116424969</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.05876112847347138</v>
+        <v>-0.4332884991851027</v>
       </c>
       <c r="CO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.04189951828595378</v>
+        <v>0.4765416548003802</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.01166103753050371</v>
+        <v>0.3643379169189024</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7558,19 +7558,19 @@
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.05352737078747735</v>
+        <v>-0.1578981380210465</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.001821849819120699</v>
+        <v>0.01831799844658477</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.07110067872425878</v>
+        <v>0.1492286021906111</v>
       </c>
       <c r="DB13" t="n">
         <v>0</v>
@@ -7585,52 +7585,52 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.04754322138464196</v>
+        <v>0.02796202521306599</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.03994494150260271</v>
+        <v>-0.1694855139372106</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-0.001631525048909809</v>
+        <v>-0.04252964264064742</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.0257624113817404</v>
+        <v>0.02117894828986998</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.02752452856745083</v>
+        <v>0.04755276822357681</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.007779903320605446</v>
+        <v>0.1548719265556689</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV13" t="n">
         <v>0</v>
@@ -7639,22 +7639,22 @@
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.004306340539590179</v>
+        <v>0.117686548807923</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.003038787745041937</v>
+        <v>-0.04399665830084392</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.008278253069756271</v>
+        <v>0.06325489064839405</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
         <v>-0</v>
@@ -7666,34 +7666,34 @@
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.02433570121183317</v>
+        <v>-0.0788397755151463</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.01016035538014561</v>
+        <v>-0.03811425111910442</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.06892601495058512</v>
+        <v>0.002211047820483288</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
       </c>
       <c r="EM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.005426649583676312</v>
+        <v>-0.03253755485123084</v>
       </c>
       <c r="EQ13" t="n">
         <v>0</v>
@@ -7702,91 +7702,91 @@
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.03971781370304182</v>
+        <v>-0.05829707478673261</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.093292732912857</v>
+        <v>0.1261409711876214</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
         <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.04550629870324319</v>
+        <v>-0.1963200572389815</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.00421929075625742</v>
+        <v>-0.01234631711778622</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.07412451157529959</v>
+        <v>0.1493137203612901</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.06407312802528131</v>
+        <v>-0.1913635443802691</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.00523951700211488</v>
+        <v>0.0671086803745503</v>
       </c>
       <c r="FL13" t="n">
-        <v>-0.03053805518936084</v>
+        <v>-0.09920638640679007</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.01085492861710668</v>
+        <v>0.07779320246846326</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.03579873566741171</v>
+        <v>0.1105064469472275</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0.01188446407079929</v>
+        <v>-0.03188245983600597</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
@@ -7795,31 +7795,31 @@
         <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.05202440932124074</v>
+        <v>-0.04148167840153111</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
         <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.03385952707118326</v>
+        <v>0.05423727580220785</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG13" t="n">
         <v>0</v>
@@ -7830,43 +7830,43 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3075097996135598</v>
+        <v>0.2829494672555192</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.08289797408379343</v>
+        <v>-0.1776411769449224</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0528533317394096</v>
+        <v>-0.03895147678075062</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1760444354264777</v>
+        <v>0.2640272431367078</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.06510957687361156</v>
+        <v>-0.1739299584008911</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0418245590682891</v>
+        <v>-0.09581553610492789</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -7881,22 +7881,22 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.07198870147729869</v>
+        <v>0.04725827305289295</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.007910862985643832</v>
+        <v>-0.03851059543212039</v>
       </c>
       <c r="W14" t="n">
-        <v>0.05217440829986784</v>
+        <v>-0.04674188956719847</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
@@ -7908,46 +7908,46 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.07041798095576833</v>
+        <v>-0.02970600080517594</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.01379288546585766</v>
+        <v>-0.1837054977209556</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.006780078360359588</v>
+        <v>-0.1247018732285401</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.006893981107993738</v>
+        <v>0.1536063161410852</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.05194997429274074</v>
+        <v>-0.09875345179198647</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.06150343491297752</v>
+        <v>0.06843529155613143</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
@@ -7965,25 +7965,25 @@
         <v>-0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.3128449043316557</v>
+        <v>0.3724277979649572</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.05907127176156755</v>
+        <v>-0.06128314224743531</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.06845799804331318</v>
+        <v>-0.2454554612848283</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
@@ -7992,49 +7992,49 @@
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.02010585929301455</v>
+        <v>-0.03491759969041625</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.05262560211835438</v>
+        <v>-0.03804754856253292</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.08911228652427812</v>
+        <v>0.04116477558543069</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL14" t="n">
         <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.0885490590193222</v>
+        <v>0.06631489109502679</v>
       </c>
       <c r="BN14" t="n">
         <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.03492960414432696</v>
+        <v>0.01311740428000263</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.1149067929714089</v>
+        <v>0.1096287934734796</v>
       </c>
       <c r="BQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
@@ -8043,46 +8043,46 @@
         <v>-0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.1428405541437046</v>
+        <v>0.286078539099304</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.06103416374692897</v>
+        <v>-0.1382064795944024</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.05259511339825992</v>
+        <v>-0.04943161588977798</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
         <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.07500211412399199</v>
+        <v>-0.113592534231006</v>
       </c>
       <c r="CF14" t="n">
         <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0.002223368120522111</v>
+        <v>0.1038758707737307</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.01079353342132621</v>
+        <v>0.04048791977410978</v>
       </c>
       <c r="CI14" t="n">
         <v>0</v>
@@ -8100,43 +8100,43 @@
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.04305780523806122</v>
+        <v>-0.21914579207995</v>
       </c>
       <c r="CO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.08380614175758765</v>
+        <v>0.2663683161195124</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.07288419866959012</v>
+        <v>0.05575560357584618</v>
       </c>
       <c r="CR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.05612494857695279</v>
+        <v>-0.0979787463617932</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.01051286095698272</v>
+        <v>0.1236956841158943</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.01309526956096678</v>
+        <v>0.03668087597173818</v>
       </c>
       <c r="DA14" t="n">
         <v>-0</v>
@@ -8145,7 +8145,7 @@
         <v>0</v>
       </c>
       <c r="DC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD14" t="n">
         <v>0</v>
@@ -8154,22 +8154,22 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.001789255809351002</v>
+        <v>0.001572576713166021</v>
       </c>
       <c r="DG14" t="n">
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.01682024214001719</v>
+        <v>0.01079600988517964</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.03058076087780952</v>
+        <v>-0.07008436817842055</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL14" t="n">
         <v>0</v>
@@ -8181,43 +8181,43 @@
         <v>-0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.04447540001083326</v>
+        <v>-0.1088246234348884</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.05692653500548193</v>
+        <v>-0.05024325224226101</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.04225106196711743</v>
+        <v>0.0154602301771199</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.01847706152733745</v>
+        <v>0.1014648095507909</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.0002793227703306174</v>
+        <v>0.05360133072694967</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.06008040542301718</v>
+        <v>-0.1162882778378823</v>
       </c>
       <c r="EB14" t="n">
         <v>0</v>
@@ -8229,22 +8229,22 @@
         <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.07007437956224245</v>
+        <v>-0.01238841810313892</v>
       </c>
       <c r="EH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.0216805141003877</v>
+        <v>0.06770791161851994</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.06058974899360964</v>
+        <v>0.07763154120792802</v>
       </c>
       <c r="EK14" t="n">
         <v>0</v>
@@ -8253,7 +8253,7 @@
         <v>-0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
         <v>-0</v>
@@ -8262,97 +8262,97 @@
         <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.04036622660075021</v>
+        <v>-0.06314575104654731</v>
       </c>
       <c r="EQ14" t="n">
         <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.02368528819930784</v>
+        <v>0.1035401335004462</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.01794754650917537</v>
+        <v>-0.03928257364516133</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW14" t="n">
         <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.05680701210764245</v>
+        <v>-0.1222910631203156</v>
       </c>
       <c r="EZ14" t="n">
         <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.004096212270214316</v>
+        <v>0.131881044934246</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.006816382166310885</v>
+        <v>0.02126715138509364</v>
       </c>
       <c r="FC14" t="n">
         <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.01449431779626665</v>
+        <v>0.007866884943277343</v>
       </c>
       <c r="FI14" t="n">
         <v>-0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.03333414687400439</v>
+        <v>0.03640551038220608</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.06675993644179021</v>
+        <v>-0.08432994343830975</v>
       </c>
       <c r="FL14" t="n">
         <v>-0</v>
       </c>
       <c r="FM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.005319310417273008</v>
+        <v>-0.001553304386518306</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
-        <v>-0.003417622058566924</v>
+        <v>0.05588605672808752</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.0002882184527518195</v>
+        <v>-0.05006714519148393</v>
       </c>
       <c r="FU14" t="n">
         <v>-0</v>
@@ -8370,22 +8370,22 @@
         <v>-0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0.001871736915185129</v>
+        <v>-0.07616565327015454</v>
       </c>
       <c r="GA14" t="n">
         <v>-0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.05057877549392156</v>
+        <v>0.08741961829564809</v>
       </c>
       <c r="GC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
         <v>0</v>
@@ -8399,16 +8399,16 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.6240077092417947</v>
+        <v>0.5192057370582217</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2019196862685658</v>
+        <v>-0.2858992403569269</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.201386282424118</v>
+        <v>0.0745501303739602</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -8426,16 +8426,16 @@
         <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4644125710139198</v>
+        <v>0.5014370014722599</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1838915420730735</v>
+        <v>-0.287144142710326</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1798124606277771</v>
+        <v>-0.01144568442705437</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -8453,49 +8453,49 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.155818605489644</v>
+        <v>0.124233185873909</v>
       </c>
       <c r="U15" t="n">
         <v>-0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0111795880564866</v>
+        <v>-0.1076558142428166</v>
       </c>
       <c r="W15" t="n">
-        <v>0.03693873853019431</v>
+        <v>-0.08469834363428337</v>
       </c>
       <c r="X15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1533393889777874</v>
+        <v>-0.05955327402276494</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.04718829055777116</v>
+        <v>-0.2644354880006904</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.06061067017625717</v>
+        <v>-0.06053234084658927</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>-0</v>
@@ -8507,22 +8507,22 @@
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.08553455350057815</v>
+        <v>0.1669465282512663</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0.03178951001111925</v>
+        <v>-0.1643801691264764</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.04690699779286359</v>
+        <v>0.1574838980717405</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
         <v>-0</v>
@@ -8534,16 +8534,16 @@
         <v>-0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.55350530082</v>
+        <v>0.5284663898723009</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.009081616303530913</v>
+        <v>-0.2689190057861477</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.09341964386953873</v>
+        <v>-0.1529364426743948</v>
       </c>
       <c r="AY15" t="n">
         <v>-0</v>
@@ -8552,7 +8552,7 @@
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
         <v>-0</v>
@@ -8561,25 +8561,25 @@
         <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.05685157259459078</v>
+        <v>-0.02610812497858481</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>-0.08496973143537678</v>
+        <v>-0.06564665501957419</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.2278571996198468</v>
+        <v>-0.005562069719519547</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
       </c>
       <c r="BI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
@@ -8588,25 +8588,25 @@
         <v>-0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.05643452134005034</v>
+        <v>-0.02775977872651718</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.04565301439226413</v>
+        <v>0.01419098510415172</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.05417426955094477</v>
+        <v>0.07544773988101552</v>
       </c>
       <c r="BQ15" t="n">
         <v>-0</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT15" t="n">
         <v>-0</v>
@@ -8615,22 +8615,22 @@
         <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.3468563643092553</v>
+        <v>0.3573021080952676</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>-0.02960831179353753</v>
+        <v>-0.1590625376783324</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.05965846174205219</v>
+        <v>-0.02304497322568115</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB15" t="n">
         <v>0</v>
@@ -8639,19 +8639,19 @@
         <v>0</v>
       </c>
       <c r="CD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.1225635062664247</v>
+        <v>-0.1570751154124663</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.04173898438971905</v>
+        <v>0.1570741528544702</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.01060216619764783</v>
+        <v>-0.01431026681733953</v>
       </c>
       <c r="CI15" t="n">
         <v>-0</v>
@@ -8663,49 +8663,49 @@
         <v>0</v>
       </c>
       <c r="CL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM15" t="n">
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.06027523766354648</v>
+        <v>-0.2079141337682877</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>-0.05778594275967829</v>
+        <v>0.3145082685356425</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.1944969420702412</v>
+        <v>0.163349954074167</v>
       </c>
       <c r="CR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS15" t="n">
         <v>-0</v>
       </c>
       <c r="CT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU15" t="n">
         <v>-0</v>
       </c>
       <c r="CV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.1089488638439297</v>
+        <v>-0.1519241311256095</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.05443790041667349</v>
+        <v>0.1645920868894127</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.01313248379032517</v>
+        <v>-0.00249231990932786</v>
       </c>
       <c r="DA15" t="n">
         <v>0</v>
@@ -8723,19 +8723,19 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.04455938998689774</v>
+        <v>-0.04408644847024536</v>
       </c>
       <c r="DG15" t="n">
         <v>-0</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.03618968848503369</v>
+        <v>0.0001842693115868311</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.001027446358978722</v>
+        <v>0.004901698741837481</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK15" t="n">
         <v>-0</v>
@@ -8747,19 +8747,19 @@
         <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.05311631307937018</v>
+        <v>-0.1209015180640732</v>
       </c>
       <c r="DP15" t="n">
         <v>-0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0.009939607463146136</v>
+        <v>0.03511046469738858</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.06399448592919321</v>
+        <v>0.02377023806863554</v>
       </c>
       <c r="DS15" t="n">
         <v>-0</v>
@@ -8774,28 +8774,28 @@
         <v>0</v>
       </c>
       <c r="DW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.0786119632065547</v>
+        <v>0.02776884443728023</v>
       </c>
       <c r="DY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0.05396902240201112</v>
+        <v>-0.05919086702314924</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.002394977419055564</v>
+        <v>0.04080265999667138</v>
       </c>
       <c r="EB15" t="n">
         <v>0</v>
       </c>
       <c r="EC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE15" t="n">
         <v>-0</v>
@@ -8804,16 +8804,16 @@
         <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.09702115180040152</v>
+        <v>-0.1563769812177165</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.04928194035325103</v>
+        <v>0.1274695935193648</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.0619347571341502</v>
+        <v>0.04156216091649624</v>
       </c>
       <c r="EK15" t="n">
         <v>-0</v>
@@ -8822,31 +8822,31 @@
         <v>-0</v>
       </c>
       <c r="EM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN15" t="n">
         <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.07277998574577668</v>
+        <v>-0.07997458047111859</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.04919306569853205</v>
+        <v>0.07754138637111675</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.03818619416619393</v>
+        <v>0.02010238335320276</v>
       </c>
       <c r="ET15" t="n">
         <v>-0</v>
       </c>
       <c r="EU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV15" t="n">
         <v>0</v>
@@ -8855,25 +8855,25 @@
         <v>-0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.1164318040261239</v>
+        <v>-0.1902210905521235</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.06614645674461953</v>
+        <v>0.173440156417609</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0.02015073287744071</v>
+        <v>-0.01377357380130975</v>
       </c>
       <c r="FC15" t="n">
         <v>-0</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
         <v>0</v>
@@ -8885,16 +8885,16 @@
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.01883663735729098</v>
+        <v>-0.09824817051025238</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.06209488728623378</v>
+        <v>0.1438915144523865</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.04109498231367242</v>
+        <v>-0.07241906082215727</v>
       </c>
       <c r="FL15" t="n">
         <v>-0</v>
@@ -8906,22 +8906,22 @@
         <v>0</v>
       </c>
       <c r="FO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP15" t="n">
         <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.01434065247845525</v>
+        <v>-0.02861340218716625</v>
       </c>
       <c r="FR15" t="n">
         <v>-0</v>
       </c>
       <c r="FS15" t="n">
-        <v>-0.19250091317909</v>
+        <v>-0.2148464044868239</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.02456805166247301</v>
+        <v>-0.01293621601368537</v>
       </c>
       <c r="FU15" t="n">
         <v>-0</v>
@@ -8930,34 +8930,34 @@
         <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX15" t="n">
         <v>0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.04834550823517372</v>
+        <v>-0.1286980461518284</v>
       </c>
       <c r="GA15" t="n">
         <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>-0.02737720484026807</v>
+        <v>0.06032264588172573</v>
       </c>
       <c r="GC15" t="n">
         <v>0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE15" t="n">
         <v>-0</v>
       </c>
       <c r="GF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG15" t="n">
         <v>-0</v>
@@ -9534,25 +9534,25 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.3685967015130235</v>
+        <v>0.3450452241720099</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2781032828360044</v>
+        <v>-0.08361281554509893</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1871242634142878</v>
+        <v>-0.1804542147469104</v>
       </c>
       <c r="G17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>-0</v>
@@ -9564,7 +9564,7 @@
         <v>-0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.24957319694019</v>
+        <v>0.5128215042339876</v>
       </c>
       <c r="L17" t="n">
         <v>-0</v>
@@ -9573,64 +9573,64 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2282400921005215</v>
+        <v>-0.1790437286917904</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1542195649825133</v>
+        <v>-0.1472367570914418</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.07018457450347945</v>
+        <v>0.09641893020300257</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.05330034571181958</v>
+        <v>-0.1235456967526464</v>
       </c>
       <c r="X17" t="n">
-        <v>0.06117650262151022</v>
+        <v>-0.04368061350540361</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.05233759805115236</v>
+        <v>-0.06862408558736675</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.009549356373882633</v>
+        <v>-0.2254777021023173</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.0309338187564397</v>
+        <v>-0.04027395969848604</v>
       </c>
       <c r="AH17" t="n">
         <v>-0</v>
@@ -9639,175 +9639,175 @@
         <v>-0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.09683126494914651</v>
+        <v>0.03361234781896185</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
         <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.01758251070048101</v>
+        <v>-0.0982851414926789</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.05953930471744975</v>
+        <v>-0.0834530471626156</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR17" t="n">
         <v>-0</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT17" t="n">
         <v>-0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.2986335560354696</v>
+        <v>0.5533963382701713</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW17" t="n">
         <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>-0.1321245746781035</v>
+        <v>-0.2067896692580772</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0.1315707527511543</v>
+        <v>-0.2304642840200786</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.05601356926332476</v>
+        <v>-0.1069694554387935</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.1659374070044568</v>
+        <v>-0.08650986593963872</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0.03398725600464286</v>
+        <v>0.01944332325636999</v>
       </c>
       <c r="BI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.1002948702207256</v>
+        <v>0.1534172078970146</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
         <v>-0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.01512619969654193</v>
+        <v>0.1315500711676189</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.05657152069048066</v>
+        <v>0.0490710766465754</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
         <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.1837466607351656</v>
+        <v>0.2929718700285279</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX17" t="n">
         <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>-0.07519229296621117</v>
+        <v>-0.1146266425831741</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.007677057413584223</v>
+        <v>-0.09891688011646825</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD17" t="n">
         <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.05204063479703097</v>
+        <v>-0.1245889614324526</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
         <v>-0</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.03314103388814345</v>
+        <v>0.09292929847326116</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.05381919783977263</v>
+        <v>0.06937240261770049</v>
       </c>
       <c r="CJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK17" t="n">
         <v>0</v>
       </c>
       <c r="CL17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM17" t="n">
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.004494574020515435</v>
+        <v>-0.2318858398329861</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
@@ -9816,106 +9816,106 @@
         <v>-0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.0001691228491215888</v>
+        <v>0.2475098098316436</v>
       </c>
       <c r="CR17" t="n">
-        <v>-0.03195012559676093</v>
+        <v>0.06064435426501856</v>
       </c>
       <c r="CS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU17" t="n">
         <v>0</v>
       </c>
       <c r="CV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.03329890515501734</v>
+        <v>-0.1183022802425677</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
         <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.0270820169801444</v>
+        <v>0.04233671931127285</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.06796782717730201</v>
+        <v>0.07274772958864027</v>
       </c>
       <c r="DB17" t="n">
         <v>0</v>
       </c>
       <c r="DC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD17" t="n">
         <v>0</v>
       </c>
       <c r="DE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.008291441077361256</v>
+        <v>-0.02245218791952602</v>
       </c>
       <c r="DG17" t="n">
         <v>0</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.01790128170127086</v>
+        <v>-0.09417923166438694</v>
       </c>
       <c r="DJ17" t="n">
-        <v>-0.009203341166130667</v>
+        <v>-0.02737009978145342</v>
       </c>
       <c r="DK17" t="n">
         <v>0</v>
       </c>
       <c r="DL17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.01210276620559145</v>
+        <v>-0.05187876005743152</v>
       </c>
       <c r="DP17" t="n">
         <v>-0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.01940626137382971</v>
+        <v>0.02639699313009083</v>
       </c>
       <c r="DS17" t="n">
-        <v>-0.08560274168158054</v>
+        <v>-0.04308978307866909</v>
       </c>
       <c r="DT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU17" t="n">
         <v>-0</v>
       </c>
       <c r="DV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW17" t="n">
         <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.002871105336872884</v>
+        <v>0.1218336520624323</v>
       </c>
       <c r="DY17" t="n">
         <v>0</v>
@@ -9924,64 +9924,64 @@
         <v>0</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.05429351826613593</v>
+        <v>-0.05423909914412281</v>
       </c>
       <c r="EB17" t="n">
-        <v>-0.0457939081856664</v>
+        <v>0.0185624761860292</v>
       </c>
       <c r="EC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE17" t="n">
         <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.04661038593707202</v>
+        <v>-0.01021627702297197</v>
       </c>
       <c r="EH17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.04708341559165653</v>
+        <v>-0.02303846332401324</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.03674264222151304</v>
+        <v>0.06349180006316504</v>
       </c>
       <c r="EL17" t="n">
         <v>-0</v>
       </c>
       <c r="EM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO17" t="n">
         <v>0</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.01862819108270855</v>
+        <v>-0.007371113637081323</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
         <v>-0</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.007460158797976154</v>
+        <v>-0.02231471817552112</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.07876338582618925</v>
+        <v>0.03997897285632839</v>
       </c>
       <c r="EU17" t="n">
         <v>-0</v>
@@ -9990,58 +9990,58 @@
         <v>0</v>
       </c>
       <c r="EW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.02865595440254024</v>
+        <v>-0.130961869778545</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
         <v>-0</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.02580813603541062</v>
+        <v>0.04864947403448976</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.06125982740231205</v>
+        <v>0.05851618218618698</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
         <v>0</v>
       </c>
       <c r="FF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG17" t="n">
         <v>0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.05052213060499685</v>
+        <v>-0.07907298580268265</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ17" t="n">
         <v>-0</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.037310979197172</v>
+        <v>0.07928852799838601</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.03327915507972417</v>
+        <v>0.03139577084248482</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
         <v>0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0.006328707842382142</v>
+        <v>-0.004941867431746272</v>
       </c>
       <c r="FR17" t="n">
         <v>-0</v>
@@ -10059,43 +10059,43 @@
         <v>-0</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.001289154298859865</v>
+        <v>0.001509790102997615</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.02075400299023397</v>
+        <v>0.09845722924614078</v>
       </c>
       <c r="FV17" t="n">
         <v>-0</v>
       </c>
       <c r="FW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>1.998861294333652e-05</v>
+        <v>-0.09484368895390273</v>
       </c>
       <c r="GA17" t="n">
         <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0.06418594864109732</v>
+        <v>0.03272558486916202</v>
       </c>
       <c r="GE17" t="n">
         <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG17" t="n">
         <v>0</v>
@@ -10103,25 +10103,25 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.2281243482239111</v>
+        <v>0.2087436268481547</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2095865753981264</v>
+        <v>-0.05022620444871806</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.06104207132619198</v>
+        <v>-0.09935825450594792</v>
       </c>
       <c r="G18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>-0</v>
@@ -10130,25 +10130,25 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1562388041903718</v>
+        <v>0.3328969505900348</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1820082288733576</v>
+        <v>-0.1149569691704018</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.04395406183515412</v>
+        <v>-0.07112990457001221</v>
       </c>
       <c r="P18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -10157,10 +10157,10 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.04051570189459024</v>
+        <v>0.04810997541919737</v>
       </c>
       <c r="U18" t="n">
         <v>-0</v>
@@ -10169,37 +10169,37 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.0231700228741305</v>
+        <v>-0.06893584262192874</v>
       </c>
       <c r="X18" t="n">
-        <v>0.05113101280701443</v>
+        <v>-0.02647222296310749</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB18" t="n">
         <v>-0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.04249312084915346</v>
+        <v>-0.02391966538341824</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.0006346762317174727</v>
+        <v>-0.145663935487152</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.02553157954635416</v>
+        <v>-0.02170840871954797</v>
       </c>
       <c r="AH18" t="n">
         <v>-0</v>
@@ -10208,28 +10208,28 @@
         <v>-0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.05442904933173712</v>
+        <v>0.02317940874953138</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.02715180319078304</v>
+        <v>-0.05539870792270061</v>
       </c>
       <c r="AP18" t="n">
-        <v>-0.02964106726429802</v>
+        <v>-0.06120207417796183</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR18" t="n">
         <v>-0</v>
@@ -10241,25 +10241,25 @@
         <v>-0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.1806722428845347</v>
+        <v>0.3614165872565684</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW18" t="n">
         <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>-0.09769339559563278</v>
+        <v>-0.08492686799106679</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0.04127175361145454</v>
+        <v>-0.1293038694721783</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
         <v>-0</v>
@@ -10268,76 +10268,76 @@
         <v>-0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.04365607663338439</v>
+        <v>-0.08564491506319886</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.1209287836300498</v>
+        <v>-0.08283967276673213</v>
       </c>
       <c r="BH18" t="n">
-        <v>-0.01382838430797467</v>
+        <v>0.01429191905609028</v>
       </c>
       <c r="BI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.07876766354683466</v>
+        <v>0.1200327356612303</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO18" t="n">
         <v>-0</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.02291199456225952</v>
+        <v>0.1128501105191308</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.04873060413921415</v>
+        <v>0.0570775751910978</v>
       </c>
       <c r="BR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS18" t="n">
         <v>0</v>
       </c>
       <c r="BT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
         <v>-0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.1126748613139538</v>
+        <v>0.1838981805095692</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX18" t="n">
         <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>-0.04893898196947579</v>
+        <v>-0.06062179444712578</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0.03737809055417811</v>
+        <v>-0.05837782940783713</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB18" t="n">
         <v>-0</v>
@@ -10346,25 +10346,25 @@
         <v>-0</v>
       </c>
       <c r="CD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.02940539454307428</v>
+        <v>-0.07261400554062765</v>
       </c>
       <c r="CF18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG18" t="n">
         <v>-0</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.0309151509785285</v>
+        <v>0.05611476707628892</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.0250411190125365</v>
+        <v>0.04694343987565708</v>
       </c>
       <c r="CJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK18" t="n">
         <v>0</v>
@@ -10376,7 +10376,7 @@
         <v>0</v>
       </c>
       <c r="CN18" t="n">
-        <v>-0.0179666522067183</v>
+        <v>-0.1630675828210429</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
@@ -10385,13 +10385,13 @@
         <v>-0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-4.561151097276335e-05</v>
+        <v>0.1324444764729082</v>
       </c>
       <c r="CR18" t="n">
-        <v>-0.01600504611219118</v>
+        <v>0.02879067237045597</v>
       </c>
       <c r="CS18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT18" t="n">
         <v>-0</v>
@@ -10400,25 +10400,25 @@
         <v>0</v>
       </c>
       <c r="CV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.01620070777641073</v>
+        <v>-0.06309914937555569</v>
       </c>
       <c r="CX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY18" t="n">
         <v>0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>0.02694675725802287</v>
+        <v>0.01909767948110712</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.03421060118063513</v>
+        <v>0.04660971944525356</v>
       </c>
       <c r="DB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC18" t="n">
         <v>0</v>
@@ -10427,52 +10427,52 @@
         <v>0</v>
       </c>
       <c r="DE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.0111150039466512</v>
+        <v>-0.01452668027046965</v>
       </c>
       <c r="DG18" t="n">
         <v>-0</v>
       </c>
       <c r="DH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI18" t="n">
-        <v>9.67782159974669e-05</v>
+        <v>-0.01753696579523888</v>
       </c>
       <c r="DJ18" t="n">
-        <v>-0.00500180872368541</v>
+        <v>-0.02543348638039615</v>
       </c>
       <c r="DK18" t="n">
         <v>0</v>
       </c>
       <c r="DL18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN18" t="n">
         <v>-0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.01380028872847735</v>
+        <v>-0.01980373356274426</v>
       </c>
       <c r="DP18" t="n">
         <v>-0</v>
       </c>
       <c r="DQ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.02775614369463671</v>
+        <v>0.006026382145859232</v>
       </c>
       <c r="DS18" t="n">
-        <v>-0.06716818585203729</v>
+        <v>-0.05053598531788007</v>
       </c>
       <c r="DT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU18" t="n">
         <v>-0</v>
@@ -10481,22 +10481,22 @@
         <v>-0</v>
       </c>
       <c r="DW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>-0.00285769519505715</v>
+        <v>0.0579127449089528</v>
       </c>
       <c r="DY18" t="n">
         <v>0</v>
       </c>
       <c r="DZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA18" t="n">
-        <v>-0.04397610274270195</v>
+        <v>-0.05319361195715743</v>
       </c>
       <c r="EB18" t="n">
-        <v>-0.04590124092600681</v>
+        <v>-0.008413616074543183</v>
       </c>
       <c r="EC18" t="n">
         <v>-0</v>
@@ -10508,22 +10508,22 @@
         <v>-0</v>
       </c>
       <c r="EF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.02769772108467808</v>
+        <v>-0.00146524569777709</v>
       </c>
       <c r="EH18" t="n">
         <v>-0</v>
       </c>
       <c r="EI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.02839591537173343</v>
+        <v>-0.01486402160731053</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.00930495645435931</v>
+        <v>0.05266698524410281</v>
       </c>
       <c r="EL18" t="n">
         <v>-0</v>
@@ -10532,55 +10532,55 @@
         <v>-0</v>
       </c>
       <c r="EN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP18" t="n">
-        <v>0.02638090981455998</v>
+        <v>-0.01013653858207145</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER18" t="n">
         <v>-0</v>
       </c>
       <c r="ES18" t="n">
-        <v>0.01403687781609319</v>
+        <v>-0.008750684730791082</v>
       </c>
       <c r="ET18" t="n">
-        <v>0.04397698384696186</v>
+        <v>0.03162016255753868</v>
       </c>
       <c r="EU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV18" t="n">
         <v>0</v>
       </c>
       <c r="EW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.01132767627824691</v>
+        <v>-0.07087907389399349</v>
       </c>
       <c r="EZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA18" t="n">
         <v>-0</v>
       </c>
       <c r="FB18" t="n">
-        <v>0.02443617732075927</v>
+        <v>0.03047268609180524</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.03524169819173556</v>
+        <v>0.03469241688644758</v>
       </c>
       <c r="FD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE18" t="n">
         <v>0</v>
@@ -10589,10 +10589,10 @@
         <v>-0</v>
       </c>
       <c r="FG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.03457294477479812</v>
+        <v>-0.04798094194722286</v>
       </c>
       <c r="FI18" t="n">
         <v>-0</v>
@@ -10601,16 +10601,16 @@
         <v>-0</v>
       </c>
       <c r="FK18" t="n">
-        <v>-0.04036628164437629</v>
+        <v>0.0399922426703772</v>
       </c>
       <c r="FL18" t="n">
-        <v>0.0198124890989361</v>
+        <v>0.007542956822042085</v>
       </c>
       <c r="FM18" t="n">
         <v>0</v>
       </c>
       <c r="FN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO18" t="n">
         <v>0</v>
@@ -10619,52 +10619,52 @@
         <v>0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>-0.00393417539551533</v>
+        <v>-0.007565920390208418</v>
       </c>
       <c r="FR18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS18" t="n">
         <v>-0</v>
       </c>
       <c r="FT18" t="n">
-        <v>0.002428762810928466</v>
+        <v>-0.003982045266174513</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.003165880712843979</v>
+        <v>0.03982841211838821</v>
       </c>
       <c r="FV18" t="n">
         <v>-0</v>
       </c>
       <c r="FW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>-0.02127528437329667</v>
+        <v>-0.05775470805684529</v>
       </c>
       <c r="GA18" t="n">
         <v>0</v>
       </c>
       <c r="GB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0.04076222859661689</v>
+        <v>0.008828075613940185</v>
       </c>
       <c r="GE18" t="n">
         <v>-0</v>
       </c>
       <c r="GF18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG18" t="n">
         <v>0</v>
